--- a/香港現在上映電影 2025-08-25.xlsx
+++ b/香港現在上映電影 2025-08-25.xlsx
@@ -256,43 +256,43 @@
     <t>2.821億</t>
   </si>
   <si>
-    <t>339.3萬</t>
+    <t>339.4萬</t>
   </si>
   <si>
     <t>15.58億</t>
   </si>
   <si>
-    <t>2.164億</t>
-  </si>
-  <si>
-    <t>6.751億</t>
+    <t>2.165億</t>
+  </si>
+  <si>
+    <t>6.753億</t>
   </si>
   <si>
     <t>38.30億</t>
   </si>
   <si>
-    <t>11.64億</t>
-  </si>
-  <si>
-    <t>47.24億</t>
+    <t>11.65億</t>
+  </si>
+  <si>
+    <t>47.25億</t>
   </si>
   <si>
     <t>11.80億</t>
   </si>
   <si>
-    <t>47.15億</t>
-  </si>
-  <si>
-    <t>6.650億</t>
+    <t>47.16億</t>
+  </si>
+  <si>
+    <t>6.651億</t>
   </si>
   <si>
     <t>2.196億</t>
   </si>
   <si>
-    <t>65.96億</t>
-  </si>
-  <si>
-    <t>8.283億</t>
+    <t>65.97億</t>
+  </si>
+  <si>
+    <t>8.285億</t>
   </si>
   <si>
     <t>97</t>
@@ -926,7 +926,7 @@
         <v>96</v>
       </c>
       <c r="G6" s="1">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H6" s="1">
         <v>73</v>
